--- a/product_selector_out/STM32L4R5-S5.xlsx
+++ b/product_selector_out/STM32L4R5-S5.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AW20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX20" s="4" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="AW21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX21" s="4" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AW22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX22" s="4" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="AW23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX23" s="4" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5525,9 +5525,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -5540,17 +5540,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5565,7 +5565,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5575,29 +5575,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -5615,22 +5615,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5645,7 +5645,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC12" s="8" t="inlineStr">
+      <c r="AC12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5655,12 +5655,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5675,7 +5675,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5685,7 +5685,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="8" t="inlineStr">
+      <c r="AK12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5730,12 +5730,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="8" t="inlineStr">
+      <c r="AT12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5745,14 +5745,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -5775,42 +5775,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5825,9 +5825,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -5867,17 +5867,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5892,7 +5892,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5902,17 +5902,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5942,22 +5942,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5972,7 +5972,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC13" s="8" t="inlineStr">
+      <c r="AC13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5982,12 +5982,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6002,7 +6002,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6012,7 +6012,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="8" t="inlineStr">
+      <c r="AK13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6057,31 +6057,31 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="7" t="inlineStr">
+      <c r="AT13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX13" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
       <c r="AY13" s="6" t="inlineStr">
         <is>
           <t>API</t>
@@ -6102,42 +6102,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6179,9 +6179,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -6194,17 +6194,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6219,7 +6219,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6229,29 +6229,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -6269,22 +6269,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6299,7 +6299,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AC14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6309,12 +6309,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6329,7 +6329,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6339,7 +6339,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="8" t="inlineStr">
+      <c r="AK14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6384,29 +6384,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -6429,42 +6429,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6479,9 +6479,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6506,9 +6506,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -6521,17 +6521,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6546,7 +6546,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6556,29 +6556,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -6596,22 +6596,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6626,7 +6626,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC15" s="8" t="inlineStr">
+      <c r="AC15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6636,12 +6636,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6656,7 +6656,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6666,7 +6666,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="8" t="inlineStr">
+      <c r="AK15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6711,29 +6711,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -6756,42 +6756,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6806,9 +6806,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6833,9 +6833,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -6848,17 +6848,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6873,7 +6873,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6883,29 +6883,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -6923,22 +6923,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6953,7 +6953,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="8" t="inlineStr">
+      <c r="AC16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6963,12 +6963,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6983,7 +6983,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6993,7 +6993,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="8" t="inlineStr">
+      <c r="AK16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7038,12 +7038,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="8" t="inlineStr">
+      <c r="AT16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7053,14 +7053,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -7083,42 +7083,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7133,9 +7133,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7175,17 +7175,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7200,7 +7200,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7210,17 +7210,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7250,22 +7250,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7280,7 +7280,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC17" s="8" t="inlineStr">
+      <c r="AC17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7290,12 +7290,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7310,7 +7310,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7320,7 +7320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="8" t="inlineStr">
+      <c r="AK17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7365,31 +7365,31 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="7" t="inlineStr">
+      <c r="AT17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
       <c r="AY17" s="6" t="inlineStr">
         <is>
           <t>API</t>
@@ -7410,42 +7410,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7487,9 +7487,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -7502,17 +7502,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7527,7 +7527,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7537,29 +7537,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -7577,22 +7577,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7607,7 +7607,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="8" t="inlineStr">
+      <c r="AC18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7617,12 +7617,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7637,7 +7637,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7647,7 +7647,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="8" t="inlineStr">
+      <c r="AK18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7692,29 +7692,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -7737,42 +7737,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
+      <c r="BC18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7787,9 +7787,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7814,9 +7814,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -7829,17 +7829,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7854,7 +7854,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7864,29 +7864,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -7904,22 +7904,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7934,7 +7934,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC19" s="8" t="inlineStr">
+      <c r="AC19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7944,12 +7944,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7964,7 +7964,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7974,7 +7974,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK19" s="8" t="inlineStr">
+      <c r="AK19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8019,12 +8019,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="8" t="inlineStr">
+      <c r="AT19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8034,14 +8034,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -8064,42 +8064,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
+      <c r="BC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8114,9 +8114,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8141,9 +8141,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -8156,17 +8156,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8181,7 +8181,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8191,29 +8191,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -8231,22 +8231,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8261,7 +8261,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC20" s="8" t="inlineStr">
+      <c r="AC20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8271,12 +8271,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8291,7 +8291,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8301,7 +8301,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="8" t="inlineStr">
+      <c r="AK20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8346,12 +8346,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU20" s="8" t="inlineStr">
+      <c r="AT20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8361,14 +8361,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -8391,42 +8391,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="8" t="inlineStr">
+      <c r="BC20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8441,9 +8441,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8468,9 +8468,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -8483,17 +8483,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8508,7 +8508,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8518,29 +8518,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -8558,22 +8558,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8588,7 +8588,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="8" t="inlineStr">
+      <c r="AC21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8598,12 +8598,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8618,7 +8618,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8628,7 +8628,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK21" s="8" t="inlineStr">
+      <c r="AK21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8673,29 +8673,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -8718,42 +8718,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="8" t="inlineStr">
+      <c r="BC21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8768,9 +8768,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8795,9 +8795,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -8810,17 +8810,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8835,7 +8835,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8845,29 +8845,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -8885,22 +8885,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8915,7 +8915,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC22" s="8" t="inlineStr">
+      <c r="AC22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8925,12 +8925,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8945,7 +8945,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8955,7 +8955,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK22" s="8" t="inlineStr">
+      <c r="AK22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9000,29 +9000,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -9045,42 +9045,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="8" t="inlineStr">
+      <c r="BC22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9095,9 +9095,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9122,9 +9122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -9137,17 +9137,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9162,7 +9162,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9172,29 +9172,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -9212,22 +9212,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9242,7 +9242,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC23" s="8" t="inlineStr">
+      <c r="AC23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9252,12 +9252,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9272,7 +9272,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9282,7 +9282,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK23" s="8" t="inlineStr">
+      <c r="AK23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9327,29 +9327,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -9372,42 +9372,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="8" t="inlineStr">
+      <c r="BC23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9422,9 +9422,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9477,7 +9477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32L4R5QI</t>
+          <t>STM32L4R5VI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9499,7 +9499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32L4R5QI</t>
+          <t>STM32L4R5VI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9536,19 +9536,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32L4R5VI</t>
+          <t>STM32L4S5VI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9565,12 +9565,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L4R5VG</t>
+          <t>STM32L4S5VI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9587,12 +9587,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L4R5VG</t>
+          <t>STM32L4S5VI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9602,403 +9602,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32L4S5AI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32L4S5AI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32L4R5QG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32L4R5QG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32L4S5VI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32L4S5VI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32L4R5ZG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32L4R5ZG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32L4S5QI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32L4S5QI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32L4R5AI</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32L4R5AI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32L4R5ZI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32L4R5ZI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32L4S5ZI</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32L4S5ZI</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32L4R5AG</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32L4R5AG</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32L4R5-S5.xlsx
+++ b/product_selector_out/STM32L4R5-S5.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -5525,9 +5525,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -5540,17 +5540,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5565,7 +5565,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5575,29 +5575,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -5615,22 +5615,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5645,7 +5645,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC12" s="7" t="inlineStr">
+      <c r="AC12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5655,12 +5655,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5675,7 +5675,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5685,7 +5685,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="7" t="inlineStr">
+      <c r="AK12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5730,12 +5730,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="7" t="inlineStr">
+      <c r="AT12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5745,14 +5745,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -5775,42 +5775,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5825,9 +5825,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -5867,17 +5867,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5892,7 +5892,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5902,17 +5902,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5942,22 +5942,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5972,7 +5972,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC13" s="7" t="inlineStr">
+      <c r="AC13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5982,12 +5982,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6002,7 +6002,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6012,7 +6012,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="7" t="inlineStr">
+      <c r="AK13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6057,17 +6057,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="7" t="inlineStr">
+      <c r="AT13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6077,7 +6077,7 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="8" t="inlineStr">
+      <c r="AX13" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -6102,42 +6102,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6179,9 +6179,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -6194,17 +6194,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6219,7 +6219,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6229,29 +6229,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -6269,22 +6269,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6299,7 +6299,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="7" t="inlineStr">
+      <c r="AC14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6309,12 +6309,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6329,7 +6329,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6339,7 +6339,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="7" t="inlineStr">
+      <c r="AK14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6384,29 +6384,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -6429,42 +6429,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6479,9 +6479,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6506,9 +6506,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -6521,17 +6521,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6546,7 +6546,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6556,29 +6556,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -6596,22 +6596,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6626,7 +6626,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC15" s="7" t="inlineStr">
+      <c r="AC15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6636,12 +6636,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6656,7 +6656,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6666,7 +6666,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="7" t="inlineStr">
+      <c r="AK15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6711,29 +6711,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -6756,42 +6756,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6806,9 +6806,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6833,9 +6833,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -6848,17 +6848,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6873,7 +6873,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6883,29 +6883,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -6923,22 +6923,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6953,7 +6953,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="7" t="inlineStr">
+      <c r="AC16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6963,12 +6963,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="7" t="inlineStr">
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6983,7 +6983,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6993,7 +6993,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="7" t="inlineStr">
+      <c r="AK16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7038,12 +7038,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="7" t="inlineStr">
+      <c r="AT16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7053,14 +7053,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -7083,42 +7083,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7133,9 +7133,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7175,17 +7175,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7200,7 +7200,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7210,17 +7210,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7250,22 +7250,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7280,7 +7280,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AC17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7290,12 +7290,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7310,7 +7310,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7320,7 +7320,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="7" t="inlineStr">
+      <c r="AK17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7365,17 +7365,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="7" t="inlineStr">
+      <c r="AT17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7385,7 +7385,7 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="8" t="inlineStr">
+      <c r="AX17" s="7" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
@@ -7410,42 +7410,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7487,9 +7487,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -7502,17 +7502,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7527,7 +7527,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7537,29 +7537,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -7577,22 +7577,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7607,7 +7607,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="7" t="inlineStr">
+      <c r="AC18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7617,12 +7617,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="7" t="inlineStr">
+      <c r="AE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7637,7 +7637,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7647,7 +7647,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="7" t="inlineStr">
+      <c r="AK18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7692,29 +7692,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -7737,42 +7737,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="7" t="inlineStr">
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7787,9 +7787,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7814,9 +7814,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -7829,17 +7829,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7854,7 +7854,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7864,29 +7864,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -7904,22 +7904,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7934,7 +7934,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC19" s="7" t="inlineStr">
+      <c r="AC19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7944,12 +7944,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="7" t="inlineStr">
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7964,7 +7964,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7974,7 +7974,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK19" s="7" t="inlineStr">
+      <c r="AK19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8019,12 +8019,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="7" t="inlineStr">
+      <c r="AT19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8034,14 +8034,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -8064,42 +8064,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="7" t="inlineStr">
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8114,9 +8114,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8141,9 +8141,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -8156,17 +8156,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8181,7 +8181,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8191,29 +8191,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -8231,22 +8231,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8261,7 +8261,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC20" s="7" t="inlineStr">
+      <c r="AC20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8271,12 +8271,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="7" t="inlineStr">
+      <c r="AE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8291,7 +8291,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="7" t="inlineStr">
+      <c r="AI20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8301,7 +8301,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="7" t="inlineStr">
+      <c r="AK20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8346,12 +8346,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU20" s="7" t="inlineStr">
+      <c r="AT20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8361,14 +8361,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -8391,42 +8391,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="7" t="inlineStr">
+      <c r="BC20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8441,9 +8441,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8468,9 +8468,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -8483,17 +8483,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8508,7 +8508,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8518,29 +8518,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -8558,22 +8558,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8588,7 +8588,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="7" t="inlineStr">
+      <c r="AC21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8598,12 +8598,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="7" t="inlineStr">
+      <c r="AE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8618,7 +8618,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="7" t="inlineStr">
+      <c r="AI21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8628,7 +8628,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK21" s="7" t="inlineStr">
+      <c r="AK21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8673,29 +8673,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -8718,42 +8718,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ21" s="7" t="inlineStr">
+      <c r="BC21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8768,9 +8768,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8795,9 +8795,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -8810,17 +8810,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8835,7 +8835,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8845,29 +8845,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -8885,22 +8885,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8915,7 +8915,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC22" s="7" t="inlineStr">
+      <c r="AC22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8925,12 +8925,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="7" t="inlineStr">
+      <c r="AE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8945,7 +8945,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="7" t="inlineStr">
+      <c r="AI22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8955,7 +8955,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK22" s="7" t="inlineStr">
+      <c r="AK22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9000,29 +9000,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -9045,42 +9045,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ22" s="7" t="inlineStr">
+      <c r="BC22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9095,9 +9095,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9122,9 +9122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -9137,17 +9137,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9162,7 +9162,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9172,29 +9172,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -9212,22 +9212,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9242,7 +9242,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC23" s="7" t="inlineStr">
+      <c r="AC23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9252,12 +9252,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="7" t="inlineStr">
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9272,7 +9272,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="7" t="inlineStr">
+      <c r="AI23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9282,7 +9282,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK23" s="7" t="inlineStr">
+      <c r="AK23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9327,29 +9327,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -9372,42 +9372,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ23" s="7" t="inlineStr">
+      <c r="BC23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9422,9 +9422,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9477,7 +9477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32L4R5VI</t>
+          <t>STM32L4R5QI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9499,7 +9499,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32L4R5VI</t>
+          <t>STM32L4R5QI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -9521,7 +9521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32L4R5VI</t>
+          <t>STM32L4R5QI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9543,7 +9543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32L4S5VI</t>
+          <t>STM32L4R5VI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9565,7 +9565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L4S5VI</t>
+          <t>STM32L4R5VI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9587,20 +9587,680 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>STM32L4R5VI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L4R5VG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L4R5VG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L4R5VG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L4S5AI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L4S5AI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L4S5AI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L4R5QG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L4R5QG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L4R5QG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>STM32L4S5VI</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L4S5VI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L4S5VI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L4R5ZG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L4R5ZG</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32L4R5ZG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L4S5QI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32L4S5QI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32L4S5QI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32L4R5AI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32L4R5AI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32L4R5AI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32L4R5ZI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32L4R5ZI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32L4R5ZI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32L4S5ZI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32L4S5ZI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32L4S5ZI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32L4R5AG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32L4R5AG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32L4R5AG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32L4R5-S5.xlsx
+++ b/product_selector_out/STM32L4R5-S5.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM23"/>
+  <dimension ref="A1:BN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.73828125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -4911,12 +4973,17 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -4937,16 +5004,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -4959,6 +5024,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -4978,7 +5044,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -5007,7 +5075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM23"/>
+  <dimension ref="A1:BN23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5075,6 +5143,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5408,6 +5477,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -5503,6 +5577,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5825,7 +5900,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6152,7 +6232,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6479,7 +6564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6806,7 +6896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7133,7 +7228,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7460,7 +7560,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7787,7 +7892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8114,7 +8224,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8441,7 +8556,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8768,7 +8888,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9095,7 +9220,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9422,7 +9552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9430,8 +9565,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
